--- a/assets/constructions/examples/ctd_sha2.xlsx
+++ b/assets/constructions/examples/ctd_sha2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,26 @@
       <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>releasepack</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
         </is>
       </c>
     </row>
@@ -687,11 +707,17 @@
           <t>2019 /Novo</t>
         </is>
       </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M16MST16040M</t>
+          <t>M16MST08060M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -701,7 +727,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST Ext-ST</t>
+          <t>ST Red-ST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -711,7 +737,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -726,13 +752,13 @@
         <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M3" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -743,16 +769,20 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>50</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -770,7 +800,7 @@
         <v>29</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -781,11 +811,17 @@
           <t>2019 /Novo</t>
         </is>
       </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M16MST10060M</t>
+          <t>M12MST08060M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -800,12 +836,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -817,16 +853,16 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="L4" t="n">
         <v>60</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -837,12 +873,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -862,13 +898,13 @@
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -879,6 +915,12 @@
           <t>2019 /Novo</t>
         </is>
       </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -977,11 +1019,17 @@
           <t>2019 /Novo</t>
         </is>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M12MST06040M</t>
+          <t>M16MST16040M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -991,17 +1039,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST Red-ST</t>
+          <t>ST Ext-ST</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M12</t>
+          <t>METRIC_THREAD:M16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M6</t>
+          <t>METRIC_THREAD:M16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1013,16 +1061,16 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>6.5</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
         <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1033,20 +1081,16 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>30</v>
-      </c>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1058,13 +1102,13 @@
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1075,6 +1119,12 @@
           <t>2019 /Novo</t>
         </is>
       </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
